--- a/Test2/03_Apriori/V2/SimsOutputs/Figures/PK_Metrics_ObsPred.xlsx
+++ b/Test2/03_Apriori/V2/SimsOutputs/Figures/PK_Metrics_ObsPred.xlsx
@@ -41,12 +41,15 @@
     <t xml:space="preserve">Fold Error AUC</t>
   </si>
   <si>
+    <t xml:space="preserve">Adalimumab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human</t>
+  </si>
+  <si>
     <t xml:space="preserve">Atezolizumab</t>
   </si>
   <si>
-    <t xml:space="preserve">Human</t>
-  </si>
-  <si>
     <t xml:space="preserve">Avelumab</t>
   </si>
   <si>
@@ -63,9 +66,6 @@
   </si>
   <si>
     <t xml:space="preserve">Tocilizumab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adalimumab</t>
   </si>
   <si>
     <t xml:space="preserve">Monkey</t>
@@ -445,25 +445,25 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D2" t="n">
-        <v>21.81</v>
+        <v>12.49</v>
       </c>
       <c r="E2" t="n">
-        <v>4361.24</v>
+        <v>1970.75</v>
       </c>
       <c r="F2" t="n">
-        <v>5837.51</v>
+        <v>2527.1</v>
       </c>
       <c r="G2" t="n">
-        <v>23.94</v>
+        <v>12.3</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1</v>
+        <v>0.98</v>
       </c>
       <c r="I2" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="3">
@@ -474,25 +474,25 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>86.5</v>
+        <v>26.57</v>
       </c>
       <c r="E3" t="n">
-        <v>15486.62</v>
+        <v>3357.26</v>
       </c>
       <c r="F3" t="n">
-        <v>17509.78</v>
+        <v>5052.23</v>
       </c>
       <c r="G3" t="n">
-        <v>71.82</v>
+        <v>24.6</v>
       </c>
       <c r="H3" t="n">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="I3" t="n">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="4">
@@ -503,25 +503,25 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>234.47</v>
+        <v>72.31</v>
       </c>
       <c r="E4" t="n">
-        <v>48072.12</v>
+        <v>10106.9</v>
       </c>
       <c r="F4" t="n">
-        <v>58148.61</v>
+        <v>15133.03</v>
       </c>
       <c r="G4" t="n">
-        <v>239.4</v>
+        <v>73.81</v>
       </c>
       <c r="H4" t="n">
         <v>1.02</v>
       </c>
       <c r="I4" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
@@ -532,25 +532,25 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>349.39</v>
+        <v>162.99</v>
       </c>
       <c r="E5" t="n">
-        <v>67350.19</v>
+        <v>22434.48</v>
       </c>
       <c r="F5" t="n">
-        <v>86959</v>
+        <v>25182.19</v>
       </c>
       <c r="G5" t="n">
-        <v>359.1</v>
+        <v>123.02</v>
       </c>
       <c r="H5" t="n">
-        <v>1.03</v>
+        <v>0.75</v>
       </c>
       <c r="I5" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="6">
@@ -561,25 +561,25 @@
         <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>559.8</v>
+        <v>295.49</v>
       </c>
       <c r="E6" t="n">
-        <v>100382.08</v>
+        <v>46446.21</v>
       </c>
       <c r="F6" t="n">
-        <v>115584.52</v>
+        <v>50165.82</v>
       </c>
       <c r="G6" t="n">
-        <v>478.79</v>
+        <v>246.05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="I6" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="7">
@@ -593,22 +593,22 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>19.19</v>
+        <v>21.81</v>
       </c>
       <c r="E7" t="n">
-        <v>906.81</v>
+        <v>4361.24</v>
       </c>
       <c r="F7" t="n">
-        <v>5000.5</v>
+        <v>5837.51</v>
       </c>
       <c r="G7" t="n">
-        <v>24.43</v>
+        <v>23.94</v>
       </c>
       <c r="H7" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="I7" t="n">
-        <v>5.51</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="8">
@@ -622,22 +622,22 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>87.5</v>
+        <v>86.5</v>
       </c>
       <c r="E8" t="n">
-        <v>6101.05</v>
+        <v>15486.62</v>
       </c>
       <c r="F8" t="n">
-        <v>15013.09</v>
+        <v>17509.78</v>
       </c>
       <c r="G8" t="n">
-        <v>73.31</v>
+        <v>71.82</v>
       </c>
       <c r="H8" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="I8" t="n">
-        <v>2.46</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="9">
@@ -651,22 +651,22 @@
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>268.8</v>
+        <v>234.47</v>
       </c>
       <c r="E9" t="n">
-        <v>33797.32</v>
+        <v>48072.12</v>
       </c>
       <c r="F9" t="n">
-        <v>49808.86</v>
+        <v>58148.61</v>
       </c>
       <c r="G9" t="n">
-        <v>244.38</v>
+        <v>239.4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.91</v>
+        <v>1.02</v>
       </c>
       <c r="I9" t="n">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="10">
@@ -677,170 +677,170 @@
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>515.58</v>
+        <v>349.39</v>
       </c>
       <c r="E10" t="n">
-        <v>48182.12</v>
+        <v>67350.19</v>
       </c>
       <c r="F10" t="n">
-        <v>98838.11</v>
+        <v>86959</v>
       </c>
       <c r="G10" t="n">
-        <v>488.76</v>
+        <v>359.1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.95</v>
+        <v>1.03</v>
       </c>
       <c r="I10" t="n">
-        <v>2.05</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>297.25</v>
+        <v>559.8</v>
       </c>
       <c r="E11" t="n">
-        <v>60623.9</v>
+        <v>100382.08</v>
       </c>
       <c r="F11" t="n">
-        <v>75958.3</v>
+        <v>115584.52</v>
       </c>
       <c r="G11" t="n">
-        <v>374.04</v>
+        <v>478.79</v>
       </c>
       <c r="H11" t="n">
-        <v>1.26</v>
+        <v>0.86</v>
       </c>
       <c r="I11" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.63</v>
+        <v>19.19</v>
       </c>
       <c r="E12" t="n">
-        <v>241.07</v>
+        <v>906.81</v>
       </c>
       <c r="F12" t="n">
-        <v>512.41</v>
+        <v>5000.5</v>
       </c>
       <c r="G12" t="n">
-        <v>2.49</v>
+        <v>24.43</v>
       </c>
       <c r="H12" t="n">
-        <v>0.95</v>
+        <v>1.27</v>
       </c>
       <c r="I12" t="n">
-        <v>2.13</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>11.87</v>
+        <v>87.5</v>
       </c>
       <c r="E13" t="n">
-        <v>1069.41</v>
+        <v>6101.05</v>
       </c>
       <c r="F13" t="n">
-        <v>1536.99</v>
+        <v>15013.09</v>
       </c>
       <c r="G13" t="n">
-        <v>7.48</v>
+        <v>73.31</v>
       </c>
       <c r="H13" t="n">
-        <v>0.63</v>
+        <v>0.84</v>
       </c>
       <c r="I13" t="n">
-        <v>1.44</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>28.52</v>
+        <v>268.8</v>
       </c>
       <c r="E14" t="n">
-        <v>3915.87</v>
+        <v>33797.32</v>
       </c>
       <c r="F14" t="n">
-        <v>5120.5</v>
+        <v>49808.86</v>
       </c>
       <c r="G14" t="n">
-        <v>24.94</v>
+        <v>244.38</v>
       </c>
       <c r="H14" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="I14" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>63.85</v>
+        <v>515.58</v>
       </c>
       <c r="E15" t="n">
-        <v>8437.95</v>
+        <v>48182.12</v>
       </c>
       <c r="F15" t="n">
-        <v>15337.53</v>
+        <v>98838.11</v>
       </c>
       <c r="G15" t="n">
-        <v>74.81</v>
+        <v>488.76</v>
       </c>
       <c r="H15" t="n">
-        <v>1.17</v>
+        <v>0.95</v>
       </c>
       <c r="I15" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="16">
@@ -851,54 +851,54 @@
         <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>158.82</v>
+        <v>297.25</v>
       </c>
       <c r="E16" t="n">
-        <v>20144.16</v>
+        <v>60623.9</v>
       </c>
       <c r="F16" t="n">
-        <v>30602.91</v>
+        <v>75958.3</v>
       </c>
       <c r="G16" t="n">
-        <v>149.62</v>
+        <v>374.04</v>
       </c>
       <c r="H16" t="n">
-        <v>0.94</v>
+        <v>1.26</v>
       </c>
       <c r="I16" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="D17" t="n">
-        <v>225.49</v>
+        <v>2.63</v>
       </c>
       <c r="E17" t="n">
-        <v>28523.18</v>
+        <v>241.07</v>
       </c>
       <c r="F17" t="n">
-        <v>50843.73</v>
+        <v>512.41</v>
       </c>
       <c r="G17" t="n">
-        <v>249.37</v>
+        <v>2.49</v>
       </c>
       <c r="H17" t="n">
-        <v>1.11</v>
+        <v>0.95</v>
       </c>
       <c r="I17" t="n">
-        <v>1.78</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="18">
@@ -909,25 +909,25 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D18" t="n">
-        <v>24.38</v>
+        <v>11.87</v>
       </c>
       <c r="E18" t="n">
-        <v>4569.73</v>
+        <v>1069.41</v>
       </c>
       <c r="F18" t="n">
-        <v>4984.05</v>
+        <v>1536.99</v>
       </c>
       <c r="G18" t="n">
-        <v>24.27</v>
+        <v>7.48</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I18" t="n">
-        <v>1.09</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="19">
@@ -938,25 +938,25 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>62.38</v>
+        <v>28.52</v>
       </c>
       <c r="E19" t="n">
-        <v>10798.56</v>
+        <v>3915.87</v>
       </c>
       <c r="F19" t="n">
-        <v>14928.83</v>
+        <v>5120.5</v>
       </c>
       <c r="G19" t="n">
-        <v>72.82</v>
+        <v>24.94</v>
       </c>
       <c r="H19" t="n">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="I19" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="20">
@@ -967,25 +967,25 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>72.64</v>
+        <v>63.85</v>
       </c>
       <c r="E20" t="n">
-        <v>12773.75</v>
+        <v>8437.95</v>
       </c>
       <c r="F20" t="n">
-        <v>19889.52</v>
+        <v>15337.53</v>
       </c>
       <c r="G20" t="n">
-        <v>97.09</v>
+        <v>74.81</v>
       </c>
       <c r="H20" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="I20" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="21">
@@ -999,22 +999,22 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>113.46</v>
+        <v>158.82</v>
       </c>
       <c r="E21" t="n">
-        <v>18520.87</v>
+        <v>20144.16</v>
       </c>
       <c r="F21" t="n">
-        <v>29787.43</v>
+        <v>30602.91</v>
       </c>
       <c r="G21" t="n">
-        <v>145.64</v>
+        <v>149.62</v>
       </c>
       <c r="H21" t="n">
-        <v>1.28</v>
+        <v>0.94</v>
       </c>
       <c r="I21" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="22">
@@ -1028,51 +1028,51 @@
         <v>10</v>
       </c>
       <c r="D22" t="n">
-        <v>207.98</v>
+        <v>225.49</v>
       </c>
       <c r="E22" t="n">
-        <v>37628.56</v>
+        <v>28523.18</v>
       </c>
       <c r="F22" t="n">
-        <v>49488.91</v>
+        <v>50843.73</v>
       </c>
       <c r="G22" t="n">
-        <v>242.73</v>
+        <v>249.37</v>
       </c>
       <c r="H22" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="I22" t="n">
-        <v>1.32</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
         <v>10</v>
       </c>
       <c r="C23" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>203.44</v>
+        <v>24.38</v>
       </c>
       <c r="E23" t="n">
-        <v>46430.5</v>
+        <v>4569.73</v>
       </c>
       <c r="F23" t="n">
-        <v>98186.06</v>
+        <v>4984.05</v>
       </c>
       <c r="G23" t="n">
-        <v>485.45</v>
+        <v>24.27</v>
       </c>
       <c r="H23" t="n">
-        <v>2.39</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>2.11</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="24">
@@ -1086,456 +1086,601 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="E24" t="e">
-        <v>#NUM!</v>
+        <v>62.38</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10798.56</v>
       </c>
       <c r="F24" t="n">
-        <v>23614.13</v>
+        <v>14928.83</v>
       </c>
       <c r="G24" t="n">
         <v>72.82</v>
       </c>
       <c r="H24" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="I24" t="e">
-        <v>#NUM!</v>
+        <v>1.17</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.38</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>382.4</v>
+        <v>72.64</v>
       </c>
       <c r="E25" t="n">
-        <v>27439.41</v>
+        <v>12773.75</v>
       </c>
       <c r="F25" t="n">
-        <v>40194.66</v>
+        <v>19889.52</v>
       </c>
       <c r="G25" t="n">
-        <v>196.83</v>
+        <v>97.09</v>
       </c>
       <c r="H25" t="n">
-        <v>0.51</v>
+        <v>1.34</v>
       </c>
       <c r="I25" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>66.14</v>
+        <v>113.46</v>
       </c>
       <c r="E26" t="n">
-        <v>5543.83</v>
+        <v>18520.87</v>
       </c>
       <c r="F26" t="n">
-        <v>6778.07</v>
+        <v>29787.43</v>
       </c>
       <c r="G26" t="n">
-        <v>79.99</v>
+        <v>145.64</v>
       </c>
       <c r="H26" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="I26" t="n">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B27" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>9.11</v>
+        <v>207.98</v>
       </c>
       <c r="E27" t="n">
-        <v>680.46</v>
+        <v>37628.56</v>
       </c>
       <c r="F27" t="n">
-        <v>1542.17</v>
+        <v>49488.91</v>
       </c>
       <c r="G27" t="n">
-        <v>12.97</v>
+        <v>242.73</v>
       </c>
       <c r="H27" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="I27" t="n">
-        <v>2.27</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D28" t="n">
-        <v>118.8</v>
+        <v>203.44</v>
       </c>
       <c r="E28" t="n">
-        <v>13895.63</v>
+        <v>46430.5</v>
       </c>
       <c r="F28" t="n">
-        <v>15388.63</v>
+        <v>98186.06</v>
       </c>
       <c r="G28" t="n">
-        <v>129.72</v>
+        <v>485.45</v>
       </c>
       <c r="H28" t="n">
-        <v>1.09</v>
+        <v>2.39</v>
       </c>
       <c r="I28" t="n">
-        <v>1.11</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C29" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>603.49</v>
-      </c>
-      <c r="E29" t="n">
-        <v>69258.05</v>
+        <v>9.08</v>
+      </c>
+      <c r="E29" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F29" t="n">
-        <v>60074.3</v>
+        <v>23614.13</v>
       </c>
       <c r="G29" t="n">
-        <v>518.88</v>
+        <v>72.82</v>
       </c>
       <c r="H29" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.87</v>
+        <v>8.02</v>
+      </c>
+      <c r="I29" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>102.19</v>
+        <v>382.4</v>
       </c>
       <c r="E30" t="n">
-        <v>3952.81</v>
+        <v>27439.41</v>
       </c>
       <c r="F30" t="n">
-        <v>11059.72</v>
+        <v>40194.66</v>
       </c>
       <c r="G30" t="n">
-        <v>132.42</v>
+        <v>196.83</v>
       </c>
       <c r="H30" t="n">
-        <v>1.3</v>
+        <v>0.51</v>
       </c>
       <c r="I30" t="n">
-        <v>2.8</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B31" t="s">
         <v>18</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>94.91</v>
+        <v>66.14</v>
       </c>
       <c r="E31" t="n">
-        <v>14000.6</v>
+        <v>5543.83</v>
       </c>
       <c r="F31" t="n">
-        <v>8958.89</v>
+        <v>6778.07</v>
       </c>
       <c r="G31" t="n">
-        <v>108.1</v>
+        <v>79.99</v>
       </c>
       <c r="H31" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="I31" t="n">
-        <v>0.64</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
         <v>18</v>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D32" t="n">
-        <v>100</v>
+        <v>9.11</v>
       </c>
       <c r="E32" t="n">
-        <v>7571.82</v>
+        <v>680.46</v>
       </c>
       <c r="F32" t="n">
-        <v>11218.34</v>
+        <v>1542.17</v>
       </c>
       <c r="G32" t="n">
-        <v>135.12</v>
+        <v>12.97</v>
       </c>
       <c r="H32" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="I32" t="n">
-        <v>1.48</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
         <v>18</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>100.73</v>
+        <v>118.8</v>
       </c>
       <c r="E33" t="n">
-        <v>6856.42</v>
+        <v>13895.63</v>
       </c>
       <c r="F33" t="n">
-        <v>6869.67</v>
+        <v>15388.63</v>
       </c>
       <c r="G33" t="n">
-        <v>81.07</v>
+        <v>129.72</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8</v>
+        <v>1.09</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
         <v>18</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D34" t="n">
-        <v>27</v>
+        <v>603.49</v>
       </c>
       <c r="E34" t="n">
-        <v>3597.1</v>
+        <v>69258.05</v>
       </c>
       <c r="F34" t="n">
-        <v>2237.29</v>
+        <v>60074.3</v>
       </c>
       <c r="G34" t="n">
-        <v>26.3</v>
+        <v>518.88</v>
       </c>
       <c r="H34" t="n">
-        <v>0.97</v>
+        <v>0.86</v>
       </c>
       <c r="I34" t="n">
-        <v>0.62</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
         <v>18</v>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>357.3</v>
+        <v>102.19</v>
       </c>
       <c r="E35" t="n">
-        <v>45092.98</v>
+        <v>3952.81</v>
       </c>
       <c r="F35" t="n">
-        <v>21970.03</v>
+        <v>11059.72</v>
       </c>
       <c r="G35" t="n">
-        <v>263.04</v>
+        <v>132.42</v>
       </c>
       <c r="H35" t="n">
-        <v>0.74</v>
+        <v>1.3</v>
       </c>
       <c r="I35" t="n">
-        <v>0.49</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B36" t="s">
         <v>18</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>19.84</v>
+        <v>94.91</v>
       </c>
       <c r="E36" t="n">
-        <v>866.91</v>
+        <v>14000.6</v>
       </c>
       <c r="F36" t="n">
-        <v>2075.32</v>
+        <v>8958.89</v>
       </c>
       <c r="G36" t="n">
-        <v>7.89</v>
+        <v>108.1</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4</v>
+        <v>1.14</v>
       </c>
       <c r="I36" t="n">
-        <v>2.39</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B37" t="s">
         <v>18</v>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>79.88</v>
+        <v>100</v>
       </c>
       <c r="E37" t="n">
-        <v>7202.3</v>
+        <v>7571.82</v>
       </c>
       <c r="F37" t="n">
-        <v>20731.65</v>
+        <v>11218.34</v>
       </c>
       <c r="G37" t="n">
-        <v>78.92</v>
+        <v>135.12</v>
       </c>
       <c r="H37" t="n">
-        <v>0.99</v>
+        <v>1.35</v>
       </c>
       <c r="I37" t="n">
-        <v>2.88</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B38" t="s">
         <v>18</v>
       </c>
       <c r="C38" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>753.22</v>
+        <v>100.73</v>
       </c>
       <c r="E38" t="n">
-        <v>62716.59</v>
+        <v>6856.42</v>
       </c>
       <c r="F38" t="n">
-        <v>202460.53</v>
+        <v>6869.67</v>
       </c>
       <c r="G38" t="n">
-        <v>789.17</v>
+        <v>81.07</v>
       </c>
       <c r="H38" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="I38" t="n">
-        <v>3.23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B39" t="s">
         <v>18</v>
       </c>
       <c r="C39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
+        <v>27</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3597.1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2237.29</v>
+      </c>
+      <c r="G39" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" t="n">
+        <v>10</v>
+      </c>
+      <c r="D40" t="n">
+        <v>357.3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>45092.98</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21970.03</v>
+      </c>
+      <c r="G40" t="n">
+        <v>263.04</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="E41" t="n">
+        <v>866.91</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2075.32</v>
+      </c>
+      <c r="G41" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="n">
+        <v>79.88</v>
+      </c>
+      <c r="E42" t="n">
+        <v>7202.3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>20731.65</v>
+      </c>
+      <c r="G42" t="n">
+        <v>78.92</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" t="n">
+        <v>30</v>
+      </c>
+      <c r="D43" t="n">
+        <v>753.22</v>
+      </c>
+      <c r="E43" t="n">
+        <v>62716.59</v>
+      </c>
+      <c r="F43" t="n">
+        <v>202460.53</v>
+      </c>
+      <c r="G43" t="n">
+        <v>789.17</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" t="n">
         <v>250.38</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E44" t="n">
         <v>8704.57</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F44" t="n">
         <v>15634.18</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G44" t="n">
         <v>266.61</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H44" t="n">
         <v>1.06</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I44" t="n">
         <v>1.8</v>
       </c>
     </row>

--- a/Test2/03_Apriori/V2/SimsOutputs/Figures/PK_Metrics_ObsPred.xlsx
+++ b/Test2/03_Apriori/V2/SimsOutputs/Figures/PK_Metrics_ObsPred.xlsx
@@ -1228,112 +1228,112 @@
         <v>10</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="E29" t="e">
-        <v>#NUM!</v>
+        <v>47.02</v>
+      </c>
+      <c r="E29" t="n">
+        <v>12369.31</v>
       </c>
       <c r="F29" t="n">
-        <v>23614.13</v>
+        <v>15745.93</v>
       </c>
       <c r="G29" t="n">
-        <v>72.82</v>
+        <v>48.55</v>
       </c>
       <c r="H29" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="I29" t="e">
-        <v>#NUM!</v>
+        <v>1.03</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>382.4</v>
+        <v>239.07</v>
       </c>
       <c r="E30" t="n">
-        <v>27439.41</v>
+        <v>55743.39</v>
       </c>
       <c r="F30" t="n">
-        <v>40194.66</v>
+        <v>78601.13</v>
       </c>
       <c r="G30" t="n">
-        <v>196.83</v>
+        <v>242.73</v>
       </c>
       <c r="H30" t="n">
-        <v>0.51</v>
+        <v>1.02</v>
       </c>
       <c r="I30" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>66.14</v>
+        <v>382.4</v>
       </c>
       <c r="E31" t="n">
-        <v>5543.83</v>
+        <v>27439.41</v>
       </c>
       <c r="F31" t="n">
-        <v>6778.07</v>
+        <v>40194.66</v>
       </c>
       <c r="G31" t="n">
-        <v>79.99</v>
+        <v>196.83</v>
       </c>
       <c r="H31" t="n">
-        <v>1.21</v>
+        <v>0.51</v>
       </c>
       <c r="I31" t="n">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B32" t="s">
         <v>18</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>9.11</v>
+        <v>66.14</v>
       </c>
       <c r="E32" t="n">
-        <v>680.46</v>
+        <v>5543.83</v>
       </c>
       <c r="F32" t="n">
-        <v>1542.17</v>
+        <v>6778.07</v>
       </c>
       <c r="G32" t="n">
-        <v>12.97</v>
+        <v>79.99</v>
       </c>
       <c r="H32" t="n">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="I32" t="n">
-        <v>2.27</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="33">
@@ -1344,25 +1344,25 @@
         <v>18</v>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D33" t="n">
-        <v>118.8</v>
+        <v>9.11</v>
       </c>
       <c r="E33" t="n">
-        <v>13895.63</v>
+        <v>680.46</v>
       </c>
       <c r="F33" t="n">
-        <v>15388.63</v>
+        <v>1542.17</v>
       </c>
       <c r="G33" t="n">
-        <v>129.72</v>
+        <v>12.97</v>
       </c>
       <c r="H33" t="n">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="I33" t="n">
-        <v>1.11</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="34">
@@ -1373,83 +1373,83 @@
         <v>18</v>
       </c>
       <c r="C34" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>603.49</v>
+        <v>118.8</v>
       </c>
       <c r="E34" t="n">
-        <v>69258.05</v>
+        <v>13895.63</v>
       </c>
       <c r="F34" t="n">
-        <v>60074.3</v>
+        <v>15388.63</v>
       </c>
       <c r="G34" t="n">
-        <v>518.88</v>
+        <v>129.72</v>
       </c>
       <c r="H34" t="n">
-        <v>0.86</v>
+        <v>1.09</v>
       </c>
       <c r="I34" t="n">
-        <v>0.87</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
         <v>18</v>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D35" t="n">
-        <v>102.19</v>
+        <v>603.49</v>
       </c>
       <c r="E35" t="n">
-        <v>3952.81</v>
+        <v>69258.05</v>
       </c>
       <c r="F35" t="n">
-        <v>11059.72</v>
+        <v>60074.3</v>
       </c>
       <c r="G35" t="n">
-        <v>132.42</v>
+        <v>518.88</v>
       </c>
       <c r="H35" t="n">
-        <v>1.3</v>
+        <v>0.86</v>
       </c>
       <c r="I35" t="n">
-        <v>2.8</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
         <v>18</v>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>94.91</v>
+        <v>102.19</v>
       </c>
       <c r="E36" t="n">
-        <v>14000.6</v>
+        <v>3952.81</v>
       </c>
       <c r="F36" t="n">
-        <v>8958.89</v>
+        <v>11059.72</v>
       </c>
       <c r="G36" t="n">
-        <v>108.1</v>
+        <v>132.42</v>
       </c>
       <c r="H36" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="I36" t="n">
-        <v>0.64</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="37">
@@ -1460,83 +1460,83 @@
         <v>18</v>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>100</v>
+        <v>94.91</v>
       </c>
       <c r="E37" t="n">
-        <v>7571.82</v>
+        <v>14000.6</v>
       </c>
       <c r="F37" t="n">
-        <v>11218.34</v>
+        <v>8958.89</v>
       </c>
       <c r="G37" t="n">
-        <v>135.12</v>
+        <v>108.1</v>
       </c>
       <c r="H37" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="I37" t="n">
-        <v>1.48</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B38" t="s">
         <v>18</v>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>100.73</v>
+        <v>100</v>
       </c>
       <c r="E38" t="n">
-        <v>6856.42</v>
+        <v>7571.82</v>
       </c>
       <c r="F38" t="n">
-        <v>6869.67</v>
+        <v>11218.34</v>
       </c>
       <c r="G38" t="n">
-        <v>81.07</v>
+        <v>135.12</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8</v>
+        <v>1.35</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B39" t="s">
         <v>18</v>
       </c>
       <c r="C39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" t="n">
+        <v>100.73</v>
+      </c>
+      <c r="E39" t="n">
+        <v>6856.42</v>
+      </c>
+      <c r="F39" t="n">
+        <v>6869.67</v>
+      </c>
+      <c r="G39" t="n">
+        <v>81.07</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I39" t="n">
         <v>1</v>
-      </c>
-      <c r="D39" t="n">
-        <v>27</v>
-      </c>
-      <c r="E39" t="n">
-        <v>3597.1</v>
-      </c>
-      <c r="F39" t="n">
-        <v>2237.29</v>
-      </c>
-      <c r="G39" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.62</v>
       </c>
     </row>
     <row r="40">
@@ -1547,54 +1547,54 @@
         <v>18</v>
       </c>
       <c r="C40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>357.3</v>
+        <v>27</v>
       </c>
       <c r="E40" t="n">
-        <v>45092.98</v>
+        <v>3597.1</v>
       </c>
       <c r="F40" t="n">
-        <v>21970.03</v>
+        <v>2237.29</v>
       </c>
       <c r="G40" t="n">
-        <v>263.04</v>
+        <v>26.3</v>
       </c>
       <c r="H40" t="n">
-        <v>0.74</v>
+        <v>0.97</v>
       </c>
       <c r="I40" t="n">
-        <v>0.49</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B41" t="s">
         <v>18</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3</v>
+        <v>10</v>
       </c>
       <c r="D41" t="n">
-        <v>19.84</v>
+        <v>357.3</v>
       </c>
       <c r="E41" t="n">
-        <v>866.91</v>
+        <v>45092.98</v>
       </c>
       <c r="F41" t="n">
-        <v>2075.32</v>
+        <v>21970.03</v>
       </c>
       <c r="G41" t="n">
-        <v>7.89</v>
+        <v>263.04</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4</v>
+        <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>2.39</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="42">
@@ -1605,25 +1605,25 @@
         <v>18</v>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="D42" t="n">
-        <v>79.88</v>
+        <v>19.84</v>
       </c>
       <c r="E42" t="n">
-        <v>7202.3</v>
+        <v>866.91</v>
       </c>
       <c r="F42" t="n">
-        <v>20731.65</v>
+        <v>2075.32</v>
       </c>
       <c r="G42" t="n">
-        <v>78.92</v>
+        <v>7.89</v>
       </c>
       <c r="H42" t="n">
-        <v>0.99</v>
+        <v>0.4</v>
       </c>
       <c r="I42" t="n">
-        <v>2.88</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="43">
@@ -1634,53 +1634,82 @@
         <v>18</v>
       </c>
       <c r="C43" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>753.22</v>
+        <v>79.88</v>
       </c>
       <c r="E43" t="n">
-        <v>62716.59</v>
+        <v>7202.3</v>
       </c>
       <c r="F43" t="n">
-        <v>202460.53</v>
+        <v>20731.65</v>
       </c>
       <c r="G43" t="n">
-        <v>789.17</v>
+        <v>78.92</v>
       </c>
       <c r="H43" t="n">
-        <v>1.05</v>
+        <v>0.99</v>
       </c>
       <c r="I43" t="n">
-        <v>3.23</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B44" t="s">
         <v>18</v>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D44" t="n">
+        <v>753.22</v>
+      </c>
+      <c r="E44" t="n">
+        <v>62716.59</v>
+      </c>
+      <c r="F44" t="n">
+        <v>202460.53</v>
+      </c>
+      <c r="G44" t="n">
+        <v>789.17</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I44" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>17</v>
+      </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" t="n">
         <v>250.38</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E45" t="n">
         <v>8704.57</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F45" t="n">
         <v>15634.18</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G45" t="n">
         <v>266.61</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H45" t="n">
         <v>1.06</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I45" t="n">
         <v>1.8</v>
       </c>
     </row>
